--- a/ValueSet-lmdi-address-type.xlsx
+++ b/ValueSet-lmdi-address-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T09:35:49+00:00</t>
+    <t>2026-03-10T12:49:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-lmdi-address-type.xlsx
+++ b/ValueSet-lmdi-address-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.7</t>
+    <t>1.0.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T12:49:22+00:00</t>
+    <t>2026-03-10T15:33:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-lmdi-address-type.xlsx
+++ b/ValueSet-lmdi-address-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T15:33:20+00:00</t>
+    <t>2026-03-18T15:02:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-lmdi-address-type.xlsx
+++ b/ValueSet-lmdi-address-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.8</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T15:02:12+00:00</t>
+    <t>2026-04-21T11:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-lmdi-address-type.xlsx
+++ b/ValueSet-lmdi-address-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T07:26:56+00:00</t>
+    <t>2026-05-11T08:19:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-lmdi-address-type.xlsx
+++ b/ValueSet-lmdi-address-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>1.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T08:19:23+00:00</t>
+    <t>2026-05-31T19:08:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-lmdi-address-type.xlsx
+++ b/ValueSet-lmdi-address-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.1</t>
+    <t>1.1.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-31T19:08:08+00:00</t>
+    <t>2026-06-12T10:49:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-lmdi-address-type.xlsx
+++ b/ValueSet-lmdi-address-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.1.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T10:49:58+00:00</t>
+    <t>2026-08-24T07:53:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
